--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/6819-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/6819-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1FCCCEB3-09C6-4080-96C6-5A0BDD54BB63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7EB1778C-2781-4052-8AE4-0D527C0DC99A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{DBA7AC29-3680-4CF9-A729-B37EBA7EBF84}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{C11B2945-7A82-4F93-8974-2B82B54E923B}"/>
   </bookViews>
   <sheets>
     <sheet name="6819-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1466,18 +1466,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7E5F42E-4DD7-442B-9596-73B745C9319C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE3933FB-2857-4B85-9A70-60EF8C7C78D5}">
   <dimension ref="A1:R28"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="8" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="9.109375" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="10.75" customWidth="1"/>
+    <col min="4" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="11.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1505,7 +1505,7 @@
       <c r="Q1" s="30"/>
       <c r="R1" s="22"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1535,7 +1535,7 @@
       <c r="Q2" s="32"/>
       <c r="R2" s="33"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1581,7 +1581,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1631,7 +1631,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="37">
         <v>2026</v>
       </c>
@@ -1685,7 +1685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>26</v>
       </c>
@@ -1741,7 +1741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="39">
         <v>2025</v>
       </c>
@@ -1795,7 +1795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
         <v>26</v>
       </c>
@@ -1851,7 +1851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>26</v>
       </c>
@@ -1907,7 +1907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>26</v>
       </c>
@@ -1963,7 +1963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="37">
         <v>2024</v>
       </c>
@@ -2017,7 +2017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>26</v>
       </c>
@@ -2073,7 +2073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>26</v>
       </c>
@@ -2129,7 +2129,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>26</v>
       </c>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="39">
         <v>2023</v>
       </c>
@@ -2239,7 +2239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
         <v>26</v>
       </c>
@@ -2295,7 +2295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="17" t="s">
         <v>26</v>
       </c>
@@ -2351,7 +2351,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="17" t="s">
         <v>26</v>
       </c>
@@ -2407,7 +2407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="37">
         <v>2022</v>
       </c>
@@ -2461,7 +2461,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
         <v>26</v>
       </c>
@@ -2517,7 +2517,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>26</v>
       </c>
@@ -2573,7 +2573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
         <v>26</v>
       </c>
@@ -2629,7 +2629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="39">
         <v>2021</v>
       </c>
@@ -2683,7 +2683,7 @@
         <v>1.48</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="17" t="s">
         <v>26</v>
       </c>
@@ -2739,7 +2739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="17" t="s">
         <v>26</v>
       </c>
@@ -2795,7 +2795,7 @@
         <v>1.48</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="37">
         <v>2020</v>
       </c>
@@ -2849,7 +2849,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>26</v>
       </c>
@@ -2905,7 +2905,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="39" t="s">
         <v>41</v>
       </c>
